--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23846,7 +23846,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24248,7 +24248,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26146,7 +26146,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31148,7 +31148,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31550,7 +31550,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -33046,7 +33046,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33448,7 +33448,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33850,7 +33850,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35346,7 +35346,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36552,7 +36552,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -38048,7 +38048,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38450,7 +38450,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38852,7 +38852,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40750,7 +40750,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41152,7 +41152,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41554,7 +41554,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42648,7 +42648,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43050,7 +43050,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43452,7 +43452,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43854,7 +43854,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44948,7 +44948,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45350,7 +45350,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45752,7 +45752,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46556,7 +46556,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47650,7 +47650,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -48052,7 +48052,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48454,7 +48454,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48856,7 +48856,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49950,7 +49950,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50352,7 +50352,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50754,7 +50754,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -51156,7 +51156,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52102,7 +52102,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52652,7 +52652,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -53054,7 +53054,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53858,7 +53858,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54952,7 +54952,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55354,7 +55354,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55756,7 +55756,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -56158,7 +56158,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -57252,7 +57252,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57654,7 +57654,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -58056,7 +58056,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58458,7 +58458,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59404,7 +59404,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59954,7 +59954,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60356,7 +60356,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60758,7 +60758,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -61160,7 +61160,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -62254,7 +62254,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62656,7 +62656,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -63058,7 +63058,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63460,7 +63460,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64554,7 +64554,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64956,7 +64956,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -65358,7 +65358,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65760,7 +65760,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66854,7 +66854,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -67256,7 +67256,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67658,7 +67658,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -68060,7 +68060,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68462,7 +68462,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69556,7 +69556,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69958,7 +69958,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -70360,7 +70360,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70762,7 +70762,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71856,7 +71856,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -72258,7 +72258,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72660,7 +72660,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -73062,7 +73062,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -74008,7 +74008,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74558,7 +74558,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74960,7 +74960,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -75362,7 +75362,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75764,7 +75764,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76858,7 +76858,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -77260,7 +77260,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77662,7 +77662,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -78064,7 +78064,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -79158,7 +79158,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79560,7 +79560,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79962,7 +79962,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -80364,7 +80364,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80766,7 +80766,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81860,7 +81860,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -82262,7 +82262,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82664,7 +82664,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -83066,7 +83066,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -84160,7 +84160,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84562,7 +84562,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84964,7 +84964,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -85366,7 +85366,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -86460,7 +86460,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86862,7 +86862,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -87264,7 +87264,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87666,7 +87666,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -88068,7 +88068,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -89162,7 +89162,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89564,7 +89564,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89966,7 +89966,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -90368,7 +90368,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">

--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23846,7 +23846,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24248,7 +24248,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26146,7 +26146,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31148,7 +31148,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31550,7 +31550,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -33046,7 +33046,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33448,7 +33448,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33850,7 +33850,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35346,7 +35346,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36552,7 +36552,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -38048,7 +38048,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38450,7 +38450,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38852,7 +38852,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40750,7 +40750,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41152,7 +41152,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41554,7 +41554,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42648,7 +42648,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43050,7 +43050,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43452,7 +43452,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43854,7 +43854,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44948,7 +44948,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45350,7 +45350,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45752,7 +45752,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46556,7 +46556,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47650,7 +47650,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -48052,7 +48052,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48454,7 +48454,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48856,7 +48856,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49950,7 +49950,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50352,7 +50352,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50754,7 +50754,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -51156,7 +51156,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52102,7 +52102,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52652,7 +52652,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -53054,7 +53054,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53858,7 +53858,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54952,7 +54952,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55354,7 +55354,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55756,7 +55756,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -56158,7 +56158,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -57252,7 +57252,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57654,7 +57654,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -58056,7 +58056,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58458,7 +58458,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59404,7 +59404,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59954,7 +59954,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60356,7 +60356,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60758,7 +60758,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -61160,7 +61160,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -62254,7 +62254,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62656,7 +62656,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -63058,7 +63058,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63460,7 +63460,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64554,7 +64554,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64956,7 +64956,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -65358,7 +65358,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65760,7 +65760,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66854,7 +66854,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -67256,7 +67256,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67658,7 +67658,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -68060,7 +68060,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68462,7 +68462,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69556,7 +69556,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69958,7 +69958,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -70360,7 +70360,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70762,7 +70762,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71856,7 +71856,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -72258,7 +72258,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72660,7 +72660,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -73062,7 +73062,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -74008,7 +74008,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74558,7 +74558,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74960,7 +74960,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -75362,7 +75362,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75764,7 +75764,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76858,7 +76858,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -77260,7 +77260,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77662,7 +77662,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -78064,7 +78064,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -79158,7 +79158,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79560,7 +79560,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79962,7 +79962,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -80364,7 +80364,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80766,7 +80766,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81860,7 +81860,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -82262,7 +82262,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82664,7 +82664,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -83066,7 +83066,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -84160,7 +84160,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84562,7 +84562,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84964,7 +84964,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -85366,7 +85366,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -86460,7 +86460,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86862,7 +86862,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -87264,7 +87264,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87666,7 +87666,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -88068,7 +88068,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -89162,7 +89162,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89564,7 +89564,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89966,7 +89966,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -90368,7 +90368,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">

--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23744,7 +23744,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27915,7 +27915,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42423,7 +42423,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44708,7 +44708,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45107,7 +45107,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48589,7 +48589,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50076,7 +50076,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50475,7 +50475,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -51814,7 +51814,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53159,7 +53159,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53558,7 +53558,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54646,7 +54646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55444,7 +55444,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -55843,7 +55843,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -56931,7 +56931,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -57729,7 +57729,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58128,7 +58128,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59068,7 +59068,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59615,7 +59615,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60014,7 +60014,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62299,7 +62299,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -62698,7 +62698,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63097,7 +63097,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -64983,7 +64983,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65382,7 +65382,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66470,7 +66470,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -66869,7 +66869,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67268,7 +67268,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69154,7 +69154,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69553,7 +69553,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -69952,7 +69952,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70351,7 +70351,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71439,7 +71439,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -71838,7 +71838,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72237,7 +72237,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -72636,7 +72636,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -73576,7 +73576,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74123,7 +74123,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74522,7 +74522,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -74921,7 +74921,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75320,7 +75320,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76408,7 +76408,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -76807,7 +76807,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77206,7 +77206,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -77605,7 +77605,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -78693,7 +78693,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79092,7 +79092,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79491,7 +79491,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -79890,7 +79890,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80289,7 +80289,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81377,7 +81377,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -81776,7 +81776,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82175,7 +82175,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -82574,7 +82574,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -83662,7 +83662,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84061,7 +84061,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84460,7 +84460,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -84859,7 +84859,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -85947,7 +85947,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86346,7 +86346,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -86745,7 +86745,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87144,7 +87144,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -87543,7 +87543,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -88631,7 +88631,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89030,7 +89030,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89429,7 +89429,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -89828,7 +89828,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">

--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23744,7 +23744,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27915,7 +27915,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42423,7 +42423,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44708,7 +44708,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45107,7 +45107,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48589,7 +48589,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50076,7 +50076,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50475,7 +50475,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -51814,7 +51814,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53159,7 +53159,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53558,7 +53558,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54646,7 +54646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55444,7 +55444,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -55843,7 +55843,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -56931,7 +56931,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -57729,7 +57729,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58128,7 +58128,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59068,7 +59068,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59615,7 +59615,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60014,7 +60014,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62299,7 +62299,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -62698,7 +62698,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63097,7 +63097,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -64983,7 +64983,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65382,7 +65382,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66470,7 +66470,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -66869,7 +66869,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67268,7 +67268,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69154,7 +69154,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69553,7 +69553,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -69952,7 +69952,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70351,7 +70351,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71439,7 +71439,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -71838,7 +71838,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72237,7 +72237,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -72636,7 +72636,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -73576,7 +73576,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74123,7 +74123,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74522,7 +74522,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -74921,7 +74921,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75320,7 +75320,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76408,7 +76408,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -76807,7 +76807,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77206,7 +77206,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -77605,7 +77605,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -78693,7 +78693,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79092,7 +79092,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79491,7 +79491,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -79890,7 +79890,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80289,7 +80289,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81377,7 +81377,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -81776,7 +81776,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82175,7 +82175,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -82574,7 +82574,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -83662,7 +83662,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84061,7 +84061,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84460,7 +84460,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -84859,7 +84859,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -85947,7 +85947,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86346,7 +86346,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -86745,7 +86745,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87144,7 +87144,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -87543,7 +87543,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -88631,7 +88631,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89030,7 +89030,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89429,7 +89429,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -89828,7 +89828,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">

--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23744,7 +23744,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27915,7 +27915,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42423,7 +42423,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44708,7 +44708,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45107,7 +45107,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48589,7 +48589,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50076,7 +50076,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50475,7 +50475,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -51814,7 +51814,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53159,7 +53159,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53558,7 +53558,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54646,7 +54646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55444,7 +55444,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -55843,7 +55843,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -56931,7 +56931,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -57729,7 +57729,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58128,7 +58128,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59068,7 +59068,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59615,7 +59615,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60014,7 +60014,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62299,7 +62299,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -62698,7 +62698,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63097,7 +63097,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -64983,7 +64983,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65382,7 +65382,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66470,7 +66470,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -66869,7 +66869,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67268,7 +67268,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69154,7 +69154,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69553,7 +69553,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -69952,7 +69952,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70351,7 +70351,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71439,7 +71439,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -71838,7 +71838,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72237,7 +72237,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -72636,7 +72636,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -73576,7 +73576,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74123,7 +74123,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74522,7 +74522,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -74921,7 +74921,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75320,7 +75320,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76408,7 +76408,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -76807,7 +76807,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77206,7 +77206,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -77605,7 +77605,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -78693,7 +78693,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79092,7 +79092,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79491,7 +79491,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -79890,7 +79890,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80289,7 +80289,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81377,7 +81377,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -81776,7 +81776,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82175,7 +82175,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -82574,7 +82574,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -83662,7 +83662,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84061,7 +84061,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84460,7 +84460,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -84859,7 +84859,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -85947,7 +85947,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86346,7 +86346,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -86745,7 +86745,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87144,7 +87144,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -87543,7 +87543,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -88631,7 +88631,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89030,7 +89030,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89429,7 +89429,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -89828,7 +89828,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">

--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23744,7 +23744,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27915,7 +27915,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42423,7 +42423,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44708,7 +44708,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45107,7 +45107,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48589,7 +48589,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50076,7 +50076,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50475,7 +50475,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -51814,7 +51814,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53159,7 +53159,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53558,7 +53558,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54646,7 +54646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55444,7 +55444,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -55843,7 +55843,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -56931,7 +56931,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -57729,7 +57729,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58128,7 +58128,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59068,7 +59068,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59615,7 +59615,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60014,7 +60014,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62299,7 +62299,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -62698,7 +62698,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63097,7 +63097,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -64983,7 +64983,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65382,7 +65382,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66470,7 +66470,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -66869,7 +66869,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67268,7 +67268,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69154,7 +69154,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69553,7 +69553,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -69952,7 +69952,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70351,7 +70351,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71439,7 +71439,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -71838,7 +71838,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72237,7 +72237,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -72636,7 +72636,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -73576,7 +73576,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74123,7 +74123,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74522,7 +74522,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -74921,7 +74921,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75320,7 +75320,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76408,7 +76408,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -76807,7 +76807,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77206,7 +77206,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -77605,7 +77605,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -78693,7 +78693,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79092,7 +79092,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79491,7 +79491,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -79890,7 +79890,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80289,7 +80289,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81377,7 +81377,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -81776,7 +81776,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82175,7 +82175,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -82574,7 +82574,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -83662,7 +83662,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84061,7 +84061,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84460,7 +84460,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -84859,7 +84859,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -85947,7 +85947,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86346,7 +86346,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -86745,7 +86745,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87144,7 +87144,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -87543,7 +87543,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -88631,7 +88631,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89030,7 +89030,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89429,7 +89429,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -89828,7 +89828,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">
